--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -35223,6 +35223,7389 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>28/01/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$176.464,44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.901,79</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.400,51</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$120,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7996</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7519</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58730</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.016.222,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$20.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>31/01/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$37.004,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.846,37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$136,68</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>827</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8377</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6840</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>68162</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.673.048,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$21.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67.308,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$17.948,96</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.923,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$179,05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>951</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6988</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8145</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>56167</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.414.814,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$22.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>07/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$200.908,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.252,04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.211,02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$89,32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10635</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8555</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75170</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.918.280,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$23.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$180.617,15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.224,97</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.791,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$112,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9491</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8162</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>69495</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.365.362,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$23.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>14/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$111.419,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$44.567,94</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.244,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.515,91</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$99,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1248</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10043</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9445</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>74971</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.909.328,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$134.830,62</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.153,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$812,72</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$85,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6462</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6755</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46940</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.925.968,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>21/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69.449,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.193,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.574,80</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>974</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$101,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9055</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8320</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>69407</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.863.392,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$25.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$58.114,33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$30.994,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.641,64</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.884,79</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$146,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>710</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7093</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5502</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>54853</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.435.712,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$26.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>28/02/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$76.778,24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.237,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.075,09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$169,26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6910</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7526</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>59042</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.958.840,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$27.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$97.470,76</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.094,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.326,13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$111,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7383</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7248</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>57643</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.295.804,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$28.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>07/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67.229,25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.801,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.391,90</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$111,54</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1308</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8920</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9745</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>62149</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.697.072,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$29.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.628,90</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.310,05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$92,21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8264</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8230</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58422</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.001.348,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$30.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>14/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$13.800,47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.179,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$94,78</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1271</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9068</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9062</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>65135</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.704.494,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$31.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$190.681,92</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.062,30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.891,68</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$88,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9728</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6965</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>67823</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.488.368,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$31.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>21/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$126.348,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$22.461,98</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.005,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$160,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8117</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6810</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>65812</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.535.338,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$32.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$224.859,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$16.656,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.946,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$160,05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7380</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6255</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>59844</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.860.602,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$32.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>28/03/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$212.595,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.724,33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.002,33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$108,04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1608</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9725</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10625</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>66441</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.074.946,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$33.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>01/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$234.015,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.500,44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.505,89</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>810</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$137,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7874</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7662</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>62403</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.154.992,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$33.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$117.623,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$31.366,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.762,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.738,28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$160,28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7868</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7281</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>60867</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.697.162,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$34.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>08/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$222.985,18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.964,18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.685,45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$117,85</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1162</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10109</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8587</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75905</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.319.428,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$34.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$22.939,21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.924,97</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$137,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9185</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8370</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>70731</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.764.100,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$35.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>15/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$28.285,79</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.972,59</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$131,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1122</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8201</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8519</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>65097</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.902.128,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$36.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>18/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$29.405,64</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.316,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$130,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1432</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8291</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11422</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>65768</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.200.694,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$37.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>22/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$183.700,54</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.205,58</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.302,01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$160,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7406</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5803</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>57642</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.024.754,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$37.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$221.732,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.692,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.820,46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>977</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$108,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9081</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8843</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>67615</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.115.980,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$38.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>29/04/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$29.282,19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.892,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>899</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$107,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>736</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8411</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6336</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>65478</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.568.384,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$38.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$76.626,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.295,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.737,56</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$103,27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9815</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7373</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75348</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.374.958,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$39.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$115.582,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.340,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.076,96</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$102,78</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9743</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7250</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>72859</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.350.010,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$40.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$23.124,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.314,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$126,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1544</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9446</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12076</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>74074</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.728.502,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$41.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$234.443,25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.015,15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.189,01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$160,17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1174</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8534</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9790</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>69512</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.391.098,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$42.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>16/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$18.308,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.047,83</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$152,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8462</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8134</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>68828</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.432.324,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$43.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$63.326,20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.127,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.435,96</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$96,65</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10553</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7949</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75443</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.679.462,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$43.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>23/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$219.960,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.517,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.137,61</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$94,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11046</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7687</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>80139</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.341.760,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$44.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$224.136,07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.068,45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.809,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$113,06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9710</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>7985</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>73635</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.249.030,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$45.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>30/05/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$254.893,69</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.720,25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.251,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$91,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1755</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12159</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11425</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>80872</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.271.220,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$60.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>03/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$82.320,56</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.390,43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.225,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$118,90</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1718</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11167</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12823</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>82042</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.115.418,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$61.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66.920,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.248,94</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.677,21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$128,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1382</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11539</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9846</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>94066</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.579.368,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$62.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>10/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$170.738,30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$68.295,32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.829,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.184,28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1132</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$129,28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1341</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11471</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11138</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>90786</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.316.834,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$63.500.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>14/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$164.891,40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$65.956,56</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.759,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.177,79</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1185</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$119,27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1860</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13270</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13011</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>97410</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.431.782,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$64.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>17/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$26.858,09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$32.229,71</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.445,48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.726,59</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$120,31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1715</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12185</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13030</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>93355</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.165.292,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$65.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$299.257,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.782,75</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.583,37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1119</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$127,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12878</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13152</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>98588</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.447.808,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>25/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24.381,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.092,51</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$123,11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1765</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13255</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>77535</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.806.214,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/06/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$292.769,27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.294,26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.712,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$158,42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1345</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9219</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10485</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75565</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.671.258,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$68.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>01/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$165.711,71</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.752,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.301,56</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$150,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1087</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10926</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9221</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>90817</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.659.686,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$69.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>04/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$348.398,90</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.734,96</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.154,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1478</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$112,24</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1557</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15285</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12029</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>113590</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.700.962,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$70.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>08/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$67.909,36</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.287,91</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.377,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$140,47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1432</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12585</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11464</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>100042</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.149.592,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$72.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$191.867,53</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.737,47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.255,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1493</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$122,39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1890</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17974</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15148</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>135140</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.971.042,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$73.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>15/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$178.823,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.358,15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.755,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1565</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$108,82</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1740</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14774</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13823</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>116616</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.965.286,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$74.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>19/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$117.484,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.607,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.311,20</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1834</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$91,51</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2304</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18696</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16215</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>136519</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.516.308,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$75.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>22/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$325.383,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.164,81</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.461,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1441</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$107,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1422</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12953</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11217</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>95722</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.829.978,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$76.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>26/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$331.694,58</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.370,99</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.322,79</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1161</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$136,04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1572</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12525</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13454</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>100316</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.074.508,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$77.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>29/07/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$37.160,55</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.286,81</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$186,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8538</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10162</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>76571</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.914.756,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$79.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$28.221,11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.791,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1109</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$151,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1160</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11684</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9630</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>97704</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.209.742,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$80.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>05/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$145.030,80</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6.138,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$986,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1139</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$121,26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2327</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12357</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18113</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>98122</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.464.038,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$81.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>07</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$337.822,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.574,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.641,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1548</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$103,91</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1952</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15094</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13976</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>108963</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.525.072,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$82.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>12/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$181.238,33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.370,03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.279,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$167,74</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10988</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9562</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>95116</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.334.866,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$83.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>16/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$58.427,22</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.166,94</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1116</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$155,33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1930</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14290</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16423</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>111410</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.082.220,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$85.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>19/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$108.312,73</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.495,12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.417,69</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1189</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$130,13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1295</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13174</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10481</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>102613</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.897.130,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$86.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>23/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$34.756,59</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.138,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$151,62</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1592</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13733</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14024</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>109369</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.392.382,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$87.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>26/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$16.870,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.727,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1223</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$145,51</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1883</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12846</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14707</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>103100</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.008.798,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$88.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>30/08/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$66.378,34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$3.206,68</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.120,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$78,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2465</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17665</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17375</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>124633</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.945.960,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$90.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$117.641,68</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$19.606,95</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.028,30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1163</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$144,50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12419</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10377</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>104043</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.407.412,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$91.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>06/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$397.972,77</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.404,52</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.895,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1234</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$153,57</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14066</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15680</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>112963</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.725.078,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$92.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>09/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$26.963,40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.258,62</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1251</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$113,68</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2064</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13162</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15077</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>99599</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.576.856,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$93.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>13/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$354.262,49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.747,23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.576,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1162</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$145,17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1606</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13957</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11817</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>106036</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.627.036,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$95.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>16/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>01</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$160.750,37</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.082,55</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.444,29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1510</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$101,38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1506</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>13351</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>11374</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>97398</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$8.817.666,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$96.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>20/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$131.152,70</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.857,51</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.615,18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1576</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$118,88</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2318</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15900</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17668</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>125020</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.015.058,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$97.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>23/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$192.061,78</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$153.649,42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.519,10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.175,88</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1814</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$90,75</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2344</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18346</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15953</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>127018</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.227.732,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$98.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35411,7 +42794,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-01-25T04:12:45+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-24T04:13:16+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42794,7 +42794,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-24T04:13:16+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-25T04:11:11+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42794,7 +42794,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-25T04:11:11+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-27T04:00:55+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42606,6 +42606,113 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>27/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>02</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$18.345,35</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.695,67</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1430</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$126,87</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1677</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15588</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12487</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>121302</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.479.624,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$99.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42794,7 +42901,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-27T04:00:55+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-28T04:14:09+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42901,7 +42901,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-28T04:14:09+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-29T04:12:18+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42713,6 +42713,113 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>30/09/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>09</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$87.537,65</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$4.863,21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$2.137,67</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1427</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$116,84</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1559</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15323</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>12133</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>113062</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$9.732.198,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$100.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42901,7 +43008,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-09-29T04:12:18+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-01T04:13:20+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42820,6 +42820,113 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>03/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>05</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$14.418,60</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.293,43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1715</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$110,86</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2738</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>17727</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>20963</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>135708</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$11.531.292,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$102.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -43008,7 +43115,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-01T04:13:20+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-06T04:12:05+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -42927,6 +42927,113 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>07/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>06</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$373.954,51</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$5.036,43</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.679,93</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1545</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$115,25</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1962</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14883</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>14704</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>115975</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.325.556,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$103.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -43115,7 +43222,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-06T04:12:05+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-11T04:12:36+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>

--- a/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
+++ b/DownloadTodosResultadosLoterias/downloads/MAIS_MILIONARIA.xlsx
@@ -43034,6 +43034,113 @@
         <x:v/>
       </x:c>
     </x:row>
+    <x:row>
+      <x:c t="n">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>11/10/2026</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>03</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>04</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$0,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$133.652,75</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$7.747,99</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$1.527,46</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$136,08</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>2096</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$50,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>15251</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$24,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>16582</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$12,00</x:v>
+      </x:c>
+      <x:c t="n">
+        <x:v>118714</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$6,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>Sim</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$10.971.744,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v>R$105.000.000,00</x:v>
+      </x:c>
+      <x:c t="str">
+        <x:v/>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -43222,7 +43329,7 @@
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-11T04:12:36+00:00</AtualizadoPeloTimerJobEm>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2026-10-12T04:12:35+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
 </file>
